--- a/experiment_results/combined_sweep/rtt_bursts_S4_atk10pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S4_atk10pct_wu500000.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>738161</t>
+          <t>445453</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>973826</t>
+          <t>528413</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1169164</t>
+          <t>640791</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1340966</t>
+          <t>700215</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1519689</t>
+          <t>819515</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1724297</t>
+          <t>904823</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1845681</t>
+          <t>940898</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1948204</t>
+          <t>1007346</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2066999</t>
+          <t>1059693</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2148886</t>
+          <t>1089233</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2214739</t>
+          <t>1125546</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2268023</t>
+          <t>1142517</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2307675</t>
+          <t>1165198</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2344648</t>
+          <t>1179491</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2374508</t>
+          <t>1195058</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2391582</t>
+          <t>1196564</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2393088</t>
+          <t>1196564</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
